--- a/data/planting_records.xlsx
+++ b/data/planting_records.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\FarmManagementSystem-single window\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -27,7 +22,7 @@
     <t>Field</t>
   </si>
   <si>
-    <t>Crop Type</t>
+    <t>Crop</t>
   </si>
   <si>
     <t>Seed Variety</t>
@@ -39,35 +34,50 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>2025-03-25</t>
-  </si>
-  <si>
-    <t>DG04001</t>
+    <t>Season</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>2025-06-24</t>
+  </si>
+  <si>
+    <t>2025-06-25</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>2025-06-28</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>DG27000</t>
+  </si>
+  <si>
+    <t>DG04000</t>
   </si>
   <si>
     <t>Sugarcane</t>
   </si>
   <si>
-    <t>97F1692</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Good seedcane used</t>
-  </si>
-  <si>
-    <t>Season</t>
-  </si>
-  <si>
-    <t>2024/25</t>
+    <t>2025/26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,7 +88,10 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,14 +140,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -422,11 +427,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -446,33 +451,122 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/planting_records.xlsx
+++ b/data/planting_records.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -22,7 +27,7 @@
     <t>Field</t>
   </si>
   <si>
-    <t>Crop</t>
+    <t>Crop Type</t>
   </si>
   <si>
     <t>Seed Variety</t>
@@ -31,53 +36,62 @@
     <t>Planted Area (ha)</t>
   </si>
   <si>
+    <t>Capitao</t>
+  </si>
+  <si>
+    <t>Planters</t>
+  </si>
+  <si>
+    <t>Choppers</t>
+  </si>
+  <si>
+    <t>Gleaners</t>
+  </si>
+  <si>
+    <t>Water Drawers</t>
+  </si>
+  <si>
+    <t>Tools Keeper</t>
+  </si>
+  <si>
+    <t>Transporters</t>
+  </si>
+  <si>
+    <t>Mandays</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
     <t>Season</t>
   </si>
   <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>2025-06-24</t>
-  </si>
-  <si>
-    <t>2025-06-25</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>2025-06-27</t>
-  </si>
-  <si>
-    <t>2025-06-28</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>DG27000</t>
-  </si>
-  <si>
-    <t>DG04000</t>
+    <t>2025-06-22</t>
+  </si>
+  <si>
+    <t>DG27004</t>
   </si>
   <si>
     <t>Sugarcane</t>
   </si>
   <si>
+    <t>R579</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>2025/26</t>
+  </si>
+  <si>
+    <t>Good seed from DG36000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +154,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -186,7 +208,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -218,9 +240,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -252,6 +275,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -427,11 +451,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,117 +494,76 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/planting_records.xlsx
+++ b/data/planting_records.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Date</t>
   </si>
@@ -36,6 +36,9 @@
     <t>Planted Area (ha)</t>
   </si>
   <si>
+    <t>Bundles Used</t>
+  </si>
+  <si>
     <t>Capitao</t>
   </si>
   <si>
@@ -69,6 +72,12 @@
     <t>2025-06-22</t>
   </si>
   <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>2025-06-24</t>
+  </si>
+  <si>
     <t>DG27004</t>
   </si>
   <si>
@@ -78,13 +87,17 @@
     <t>R579</t>
   </si>
   <si>
-    <t>0</t>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>Good seed from DG36000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The real figures at Transporters were two, but we added one manday on light duty du to injury and was assigned to planting activities_x000D_
+</t>
   </si>
   <si>
     <t>2025/26</t>
-  </si>
-  <si>
-    <t>Good seed from DG36000</t>
   </si>
 </sst>
 </file>
@@ -452,27 +465,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,52 +514,155 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>8.5</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>17</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>19</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="O2" t="s">
+      <c r="E3">
+        <v>1.83</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
         <v>20</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>12.5</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>25</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>51</v>
+      </c>
+      <c r="O4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/planting_records.xlsx
+++ b/data/planting_records.xlsx
@@ -93,11 +93,10 @@
     <t>Good seed from DG36000</t>
   </si>
   <si>
-    <t xml:space="preserve">The real figures at Transporters were two, but we added one manday on light duty du to injury and was assigned to planting activities_x000D_
-</t>
-  </si>
-  <si>
     <t>2025/26</t>
+  </si>
+  <si>
+    <t>The real figures at Transporters were two, but we added one manday on light duty due to injury and was assigned to planting activitie</t>
   </si>
 </sst>
 </file>
@@ -565,7 +564,7 @@
         <v>23</v>
       </c>
       <c r="P2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -612,7 +611,7 @@
         <v>34</v>
       </c>
       <c r="P3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -659,10 +658,10 @@
         <v>51</v>
       </c>
       <c r="O4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" t="s">
         <v>24</v>
-      </c>
-      <c r="P4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/planting_records.xlsx
+++ b/data/planting_records.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Season</t>
   </si>
   <si>
-    <t>2025-06-22</t>
-  </si>
-  <si>
     <t>2025-06-23</t>
   </si>
   <si>
@@ -87,9 +84,6 @@
     <t>R579</t>
   </si>
   <si>
-    <t>1.38</t>
-  </si>
-  <si>
     <t>Good seed from DG36000</t>
   </si>
   <si>
@@ -97,12 +91,84 @@
   </si>
   <si>
     <t>The real figures at Transporters were two, but we added one manday on light duty due to injury and was assigned to planting activitie</t>
+  </si>
+  <si>
+    <t>2025-06-25</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>2025-06-28</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>DG27003</t>
+  </si>
+  <si>
+    <t>DG27002</t>
+  </si>
+  <si>
+    <t>DG27001</t>
+  </si>
+  <si>
+    <t>2025-07-7</t>
+  </si>
+  <si>
+    <t>2025-07-8</t>
+  </si>
+  <si>
+    <t>2025-07-9</t>
+  </si>
+  <si>
+    <t>2025-07-1</t>
+  </si>
+  <si>
+    <t>2025-07-2</t>
+  </si>
+  <si>
+    <t>2025-07-3</t>
+  </si>
+  <si>
+    <t>2025-07-4</t>
+  </si>
+  <si>
+    <t>2025-07-5</t>
+  </si>
+  <si>
+    <t>2025-07-6</t>
+  </si>
+  <si>
+    <t>DG04006</t>
+  </si>
+  <si>
+    <t>DG04005</t>
+  </si>
+  <si>
+    <t>DG04004</t>
+  </si>
+  <si>
+    <t>DG04003</t>
+  </si>
+  <si>
+    <t>DG04002</t>
+  </si>
+  <si>
+    <t>DG04001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -155,11 +221,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,8 +533,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" customWidth="1"/>
+    <col min="16" max="16" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -522,34 +609,34 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="F2">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -558,13 +645,13 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -572,75 +659,78 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>51</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
       </c>
       <c r="P3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3.01</v>
       </c>
       <c r="F4">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="I4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -655,14 +745,979 @@
         <v>3</v>
       </c>
       <c r="N4">
-        <v>51</v>
-      </c>
-      <c r="O4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="P4" t="s">
-        <v>24</v>
-      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.42</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>6</v>
+      </c>
+      <c r="P6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.31</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>27</v>
+      </c>
+      <c r="P7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>20</v>
+      </c>
+      <c r="I8">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <v>49</v>
+      </c>
+      <c r="O8" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1.64</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9">
+        <v>47</v>
+      </c>
+      <c r="O9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1.466</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>16</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>34</v>
+      </c>
+      <c r="O10" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.03</v>
+      </c>
+      <c r="F12" s="3">
+        <v>5.15</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>15</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="F13" s="3">
+        <v>10.149999999999999</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>9</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>20</v>
+      </c>
+      <c r="O13" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>10</v>
+      </c>
+      <c r="P14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1.18</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5.8999999999999995</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>12</v>
+      </c>
+      <c r="O15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="F16" s="3">
+        <v>5.45</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>11</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.25</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>7</v>
+      </c>
+      <c r="O17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F18" s="3">
+        <v>12.25</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>13</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>26</v>
+      </c>
+      <c r="O18" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2.54</v>
+      </c>
+      <c r="F19" s="3">
+        <v>12.7</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>13</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>27</v>
+      </c>
+      <c r="O19" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>6</v>
+      </c>
+      <c r="P20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.77</v>
+      </c>
+      <c r="F21" s="3">
+        <v>8.85</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>20</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1.38</v>
+      </c>
+      <c r="F22" s="3">
+        <v>6.8999999999999995</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>6</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>15</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E30" s="2"/>
+      <c r="F30" s="4"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E31" s="2"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E32" s="2"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E33" s="2"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E34" s="2"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E35" s="2"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E36" s="2"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E37" s="2"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E38" s="2"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E39" s="2"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E40" s="2"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E41" s="2"/>
+      <c r="F41" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
